--- a/Documentacion/Drivers-Arquitectonicos/EscenariosCalidad.xlsx
+++ b/Documentacion/Drivers-Arquitectonicos/EscenariosCalidad.xlsx
@@ -1509,7 +1509,7 @@
     <t>un administrador de la empresa, con el operador de la plataforma exige que los datos de la empresa permanezcan en su propia infraestructura, sobre el paquete de despliegue del sistema y la base de datos de esa empresa, en la puesta en marcha de un cliente nuevo. El sistema se instala en la infraestructura indicada usando el mismo paquete, sin cambios en el código, con 0 cambios de código entre el despliegue en nube y en sitio, puesta en marcha en 7 días o menos (tope de retraso operativo) y 100% de las funciones disponibles en ambos modos.</t>
   </si>
   <si>
-    <t>Contradice la decisión vigente de SaaS multi-tenant operado por el equipo. Se replanteó como independencia del proveedor y se deja marcado para decisión del equipo.</t>
+    <t>Se replanteó como independencia del proveedor. La observación de que contradecía el modelo multi-tenant quedó sin efecto: ese modelo se descartó y hoy manda ADR-001, que decide entrega local-first con una instalación por empresa. Es justo lo que este escenario pide, así que ya no hay nada que decidir.</t>
   </si>
   <si>
     <t>ESC-17</t>
@@ -1911,7 +1911,7 @@
     <t>el operador de la plataforma recibe el reporte de un fallo en un dispositivo o en la sincronización, sobre los registros de operación, la telemetría y el estado de sincronización, en soporte remoto, con la finca a horas de distancia. El sistema permite identificar la causa con la información de operación disponible, sin acceder al contenido de producción del cliente, con causa identificada en 4 horas o menos en el 80% de los casos, 0 desplazamientos para diagnóstico y 0 accesos a datos de negocio del cliente.</t>
   </si>
   <si>
-    <t>Se replanteó agregando la restricción de aislamiento del SaaS: soporte remoto sí, lectura de los datos del cliente no.</t>
+    <t>Se replanteó agregando la restricción de aislamiento entre empresas (ADR-003): soporte remoto sí, lectura de los datos del cliente no.</t>
   </si>
   <si>
     <t>ESC-31</t>
@@ -2190,7 +2190,7 @@
     <t>cualquier usuario, incluido el operador de la plataforma intenta modificar o borrar una entrada de la bitácora, sobre la bitácora de eventos del sistema, en operación normal y también durante mantenimiento o soporte. El sistema impide la operación y registra el intento, con 0 entradas modificadas o borradas, 100% de los intentos registrados e integridad de la bitácora verificable en cada respaldo.</t>
   </si>
   <si>
-    <t>Se replanteó incluyendo al operador de la plataforma, que es el caso difícil en un SaaS y el que el planteamiento original dejaba fuera.</t>
+    <t>Se replanteó incluyendo al operador de la plataforma, que es el caso difícil cuando el proveedor opera la instalación del cliente, y el que el planteamiento original dejaba fuera.</t>
   </si>
   <si>
     <t>ESC-41</t>
@@ -2256,7 +2256,7 @@
     <t>el almacenamiento en línea e histórico de esa empresa</t>
   </si>
   <si>
-    <t>en la operación del SaaS con varias empresas, bajo el presupuesto de ~20.000 USD de construcción y puesta en marcha</t>
+    <t>en la operación local-first, con una instalación por empresa, bajo el presupuesto de ~20.000 USD de construcción y puesta en marcha</t>
   </si>
   <si>
     <t>mueve automáticamente lo más antiguo a almacenamiento de menor costo, conservándolo obtenible</t>
@@ -2265,7 +2265,7 @@
     <t>crecimiento del costo por finca sublineal frente al crecimiento de datos, 0 datos eliminados y movimiento automático sin intervención manual</t>
   </si>
   <si>
-    <t>el operador de la plataforma observa que la historia de una empresa creció un año más, sobre el almacenamiento en línea e histórico de esa empresa, en la operación del SaaS con varias empresas, bajo el presupuesto de ~20.000 USD de construcción y puesta en marcha. El sistema mueve automáticamente lo más antiguo a almacenamiento de menor costo, conservándolo obtenible, con crecimiento del costo por finca sublineal frente al crecimiento de datos, 0 datos eliminados y movimiento automático sin intervención manual.</t>
+    <t>el operador de la plataforma observa que la historia de una empresa creció un año más, sobre el almacenamiento en línea e histórico de esa empresa, en la operación local-first, con una instalación por empresa, bajo el presupuesto de ~20.000 USD de construcción y puesta en marcha. El sistema mueve automáticamente lo más antiguo a almacenamiento de menor costo, conservándolo obtenible, con crecimiento del costo por finca sublineal frente al crecimiento de datos, 0 datos eliminados y movimiento automático sin intervención manual.</t>
   </si>
   <si>
     <t>Se replanteó como escenario del operador, que es quien paga el almacenamiento, apoyado en la concesión de ESC-42.</t>
@@ -2451,7 +2451,7 @@
     <t>la base de datos de la empresa y sus respaldos cifrados</t>
   </si>
   <si>
-    <t>en la operación normal del SaaS, con clientes que compiten entre sí</t>
+    <t>en la operación normal de la instalación de cada empresa, con clientes que compiten entre sí</t>
   </si>
   <si>
     <t>permite la tarea sin exponer el contenido de negocio y registra todo acceso</t>
@@ -2460,7 +2460,7 @@
     <t>0 accesos a datos de negocio en operación normal, 100% de los accesos excepcionales registrados y autorizados y respaldos cifrados en el 100% de los casos</t>
   </si>
   <si>
-    <t>el operador de la plataforma (el equipo FlorLogic) ejecuta una tarea de operación (respaldo, restauración, despliegue o diagnóstico), sobre la base de datos de la empresa y sus respaldos cifrados, en la operación normal del SaaS, con clientes que compiten entre sí. El sistema permite la tarea sin exponer el contenido de negocio y registra todo acceso, con 0 accesos a datos de negocio en operación normal, 100% de los accesos excepcionales registrados y autorizados y respaldos cifrados en el 100% de los casos.</t>
+    <t>el operador de la plataforma (el equipo FlorLogic) ejecuta una tarea de operación (respaldo, restauración, despliegue o diagnóstico), sobre la base de datos de la empresa y sus respaldos cifrados, en la operación normal de la instalación de cada empresa, con clientes que compiten entre sí. El sistema permite la tarea sin exponer el contenido de negocio y registra todo acceso, con 0 accesos a datos de negocio en operación normal, 100% de los accesos excepcionales registrados y autorizados y respaldos cifrados en el 100% de los casos.</t>
   </si>
   <si>
     <t>Es el escenario que obliga a decidir de quién es la clave de cifrado de los respaldos. Se dejó explícito porque también va al contrato.</t>
@@ -2514,7 +2514,7 @@
     <t>un administrador de la empresa o el operador de la plataforma da de alta una finca nueva de una empresa ya existente, sobre la estructura de la empresa (fincas, bloques, naves, camas y secciones), en operación normal, sin detener a las fincas existentes. El sistema deja la finca operativa con su catálogo y sus usuarios, sin reinstalar ni reconfigurar el sistema, con alta completa en 1 día o menos, 0 reinstalaciones y 0 minutos de interrupción para las fincas existentes.</t>
   </si>
   <si>
-    <t>Se replanteó como escalabilidad horizontal dentro de una empresa, distinta del alta de un cliente nuevo del SaaS.</t>
+    <t>Se replanteó como escalabilidad horizontal dentro de una empresa, distinta del alta de un cliente nuevo, que en el modelo local-first es una instalación aparte (ADR-001, ADR-016).</t>
   </si>
   <si>
     <t>ESC-53</t>
